--- a/files/九龙-红磡-悦麓.xlsx
+++ b/files/九龙-红磡-悦麓.xlsx
@@ -5502,12 +5502,12 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7071,12 +7071,12 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 283呎 (1房)
 $623万
 $22,008/呎
-(在售)</t>
+(26年-09月-05日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">

--- a/files/九龙-红磡-悦麓.xlsx
+++ b/files/九龙-红磡-悦麓.xlsx
@@ -5507,7 +5507,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -7076,7 +7076,7 @@
           <t>B | 283呎 (1房)
 $623万
 $22,008/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
